--- a/真题/考点分布.xlsx
+++ b/真题/考点分布.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\HIT837\HIT837-Book-of-Answer\真题\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C2767F4-C1E4-455C-8EDE-BCAB4F7C7302}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B519EAE1-0257-4683-89B8-BA5366D898B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{483410DF-229B-F841-A2F7-CB7B2A2D44F9}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13320" xr2:uid="{483410DF-229B-F841-A2F7-CB7B2A2D44F9}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="236">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="260">
   <si>
     <t>考频</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -975,6 +975,101 @@
   </si>
   <si>
     <t>837资料库</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>各层功能，设备，协议</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RIP是什么类型的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ipv6地址长度</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DNS查询方式 域名结构</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SMTP在哪一层</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>时延计算 MTU</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>子网划分</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>快重传、字段功能</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">connect API </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>分组、序列密码，密码体系</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>属性有哪些</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Needham-Schroeder 第三方认证</t>
+  </si>
+  <si>
+    <t>GB/T 22239-2019纵深防御</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CA中心和数字证书的关系</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>简述数字签名的工作流程</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> 主机防火墙应用与独立防火墙</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ipsec协议</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dh计算</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SVM核函数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>辨析</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> DMA 机制</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> SYN Flood ， DoS（拒绝服务攻击）和DDoS（分布式拒绝服务攻击）区别</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>栈溢出攻击概念</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AC计算</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1084,7 +1179,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="15">
+  <fills count="16">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1169,6 +1264,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="3">
     <border>
@@ -1205,7 +1306,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1254,13 +1355,55 @@
     <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -1269,12 +1412,12 @@
     <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1284,47 +1427,14 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1645,115 +1755,115 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:U109"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="61.25" customWidth="1"/>
-    <col min="3" max="3" width="6.75" style="12" customWidth="1"/>
-    <col min="4" max="4" width="25.25" customWidth="1"/>
+    <col min="2" max="2" width="61.265625" customWidth="1"/>
+    <col min="3" max="3" width="6.73046875" style="12" customWidth="1"/>
+    <col min="4" max="4" width="25.265625" customWidth="1"/>
     <col min="5" max="5" width="33" customWidth="1"/>
-    <col min="6" max="6" width="22.875" customWidth="1"/>
-    <col min="7" max="7" width="19.25" customWidth="1"/>
-    <col min="8" max="8" width="34.125" customWidth="1"/>
+    <col min="6" max="6" width="22.86328125" customWidth="1"/>
+    <col min="7" max="7" width="19.265625" customWidth="1"/>
+    <col min="8" max="8" width="34.1328125" customWidth="1"/>
     <col min="9" max="9" width="37" customWidth="1"/>
-    <col min="10" max="10" width="39.75" customWidth="1"/>
-    <col min="11" max="11" width="58.875" customWidth="1"/>
-    <col min="12" max="12" width="108.75" customWidth="1"/>
+    <col min="10" max="10" width="39.73046875" customWidth="1"/>
+    <col min="11" max="11" width="58.86328125" customWidth="1"/>
+    <col min="12" max="12" width="108.73046875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A1" s="23" t="s">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A1" s="37" t="s">
         <v>219</v>
       </c>
-      <c r="B1" s="23"/>
+      <c r="B1" s="37"/>
       <c r="C1" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="16">
+      <c r="D1" s="17">
         <v>2018</v>
       </c>
-      <c r="E1" s="16">
+      <c r="E1" s="17">
         <v>2019</v>
       </c>
-      <c r="F1" s="16">
+      <c r="F1" s="17">
         <v>2020</v>
       </c>
-      <c r="G1" s="16">
+      <c r="G1" s="17">
         <v>2021</v>
       </c>
-      <c r="H1" s="16">
+      <c r="H1" s="17">
         <v>2022</v>
       </c>
-      <c r="I1" s="16">
+      <c r="I1" s="17">
         <v>2023</v>
       </c>
-      <c r="J1" s="16">
+      <c r="J1" s="17">
         <v>2024</v>
       </c>
-      <c r="K1" s="16">
+      <c r="K1" s="17">
         <v>2025</v>
       </c>
-      <c r="L1" s="16">
+      <c r="L1" s="17">
         <v>2026</v>
       </c>
-      <c r="M1" s="16"/>
-      <c r="N1" s="16"/>
-      <c r="O1" s="16"/>
-      <c r="P1" s="16"/>
-      <c r="Q1" s="16"/>
-      <c r="R1" s="16"/>
-      <c r="S1" s="16"/>
-      <c r="T1" s="16"/>
-      <c r="U1" s="16"/>
-    </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A2" s="24"/>
-      <c r="B2" s="24"/>
+      <c r="M1" s="17"/>
+      <c r="N1" s="17"/>
+      <c r="O1" s="17"/>
+      <c r="P1" s="17"/>
+      <c r="Q1" s="17"/>
+      <c r="R1" s="17"/>
+      <c r="S1" s="17"/>
+      <c r="T1" s="17"/>
+      <c r="U1" s="17"/>
+    </row>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A2" s="38"/>
+      <c r="B2" s="38"/>
       <c r="C2" s="11" t="s">
         <v>187</v>
       </c>
-      <c r="D2" s="16"/>
-      <c r="E2" s="16"/>
-      <c r="F2" s="16"/>
-      <c r="G2" s="16"/>
-      <c r="H2" s="16"/>
-      <c r="I2" s="16"/>
-      <c r="J2" s="16"/>
-      <c r="K2" s="16"/>
-      <c r="L2" s="16"/>
-      <c r="M2" s="16"/>
-      <c r="N2" s="16"/>
-      <c r="O2" s="16"/>
-      <c r="P2" s="16"/>
-      <c r="Q2" s="16"/>
-      <c r="R2" s="16"/>
-      <c r="S2" s="16"/>
-      <c r="T2" s="16"/>
-      <c r="U2" s="16"/>
-    </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A3" s="21" t="s">
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="17"/>
+      <c r="H2" s="17"/>
+      <c r="I2" s="17"/>
+      <c r="J2" s="17"/>
+      <c r="K2" s="17"/>
+      <c r="L2" s="17"/>
+      <c r="M2" s="17"/>
+      <c r="N2" s="17"/>
+      <c r="O2" s="17"/>
+      <c r="P2" s="17"/>
+      <c r="Q2" s="17"/>
+      <c r="R2" s="17"/>
+      <c r="S2" s="17"/>
+      <c r="T2" s="17"/>
+      <c r="U2" s="17"/>
+    </row>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A3" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="21"/>
+      <c r="B3" s="36"/>
       <c r="C3" s="11"/>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A4" s="22"/>
-      <c r="B4" s="22"/>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A4" s="27"/>
+      <c r="B4" s="27"/>
       <c r="C4" s="11"/>
     </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A5" s="16" t="s">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A5" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="16"/>
+      <c r="B5" s="17"/>
       <c r="C5" s="11"/>
     </row>
-    <row r="6" spans="1:21" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="19" t="s">
+    <row r="6" spans="1:21" s="5" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="B6" s="19"/>
+      <c r="B6" s="33"/>
       <c r="C6" s="11">
         <f>COUNTA(D6:U6)</f>
         <v>1</v>
@@ -1762,14 +1872,14 @@
         <v>175</v>
       </c>
     </row>
-    <row r="7" spans="1:21" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="19" t="s">
+    <row r="7" spans="1:21" s="5" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="33" t="s">
         <v>3</v>
       </c>
-      <c r="B7" s="19"/>
+      <c r="B7" s="33"/>
       <c r="C7" s="11">
         <f t="shared" ref="C7:C70" si="0">COUNTA(D7:U7)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D7" s="5" t="s">
         <v>82</v>
@@ -1786,15 +1896,18 @@
       <c r="K7" s="5" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="8" spans="1:21" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="20" t="s">
+      <c r="L7" s="5" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" s="13" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="34" t="s">
         <v>4</v>
       </c>
-      <c r="B8" s="20"/>
+      <c r="B8" s="34"/>
       <c r="C8" s="11">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D8" s="13" t="s">
         <v>101</v>
@@ -1814,12 +1927,15 @@
       <c r="K8" s="13" t="s">
         <v>190</v>
       </c>
-    </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A9" s="16" t="s">
+      <c r="L8" s="13" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A9" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="B9" s="16"/>
+      <c r="B9" s="17"/>
       <c r="C9" s="11">
         <f t="shared" si="0"/>
         <v>2</v>
@@ -1831,11 +1947,11 @@
         <v>120</v>
       </c>
     </row>
-    <row r="10" spans="1:21" s="5" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="19" t="s">
+    <row r="10" spans="1:21" s="5" customFormat="1" ht="14.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="33" t="s">
         <v>22</v>
       </c>
-      <c r="B10" s="19"/>
+      <c r="B10" s="33"/>
       <c r="C10" s="11">
         <f t="shared" si="0"/>
         <v>2</v>
@@ -1847,14 +1963,14 @@
         <v>194</v>
       </c>
     </row>
-    <row r="11" spans="1:21" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="20" t="s">
+    <row r="11" spans="1:21" s="13" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="34" t="s">
         <v>5</v>
       </c>
-      <c r="B11" s="20"/>
+      <c r="B11" s="34"/>
       <c r="C11" s="11">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E11" s="13" t="s">
         <v>107</v>
@@ -1877,25 +1993,31 @@
       <c r="K11" s="13" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="12" spans="1:21" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="26" t="s">
+      <c r="L11" s="13" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21" s="6" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="35" t="s">
         <v>6</v>
       </c>
-      <c r="B12" s="26"/>
+      <c r="B12" s="35"/>
       <c r="C12" s="11">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K12" s="6" t="s">
         <v>191</v>
       </c>
-    </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A13" s="16" t="s">
+      <c r="L12" s="6" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A13" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="B13" s="16"/>
+      <c r="B13" s="17"/>
       <c r="C13" s="11">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -1904,11 +2026,11 @@
         <v>155</v>
       </c>
     </row>
-    <row r="14" spans="1:21" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="19" t="s">
+    <row r="14" spans="1:21" s="5" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="33" t="s">
         <v>7</v>
       </c>
-      <c r="B14" s="19"/>
+      <c r="B14" s="33"/>
       <c r="C14" s="11">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -1926,14 +2048,14 @@
         <v>188</v>
       </c>
     </row>
-    <row r="15" spans="1:21" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="20" t="s">
+    <row r="15" spans="1:21" s="13" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="34" t="s">
         <v>8</v>
       </c>
-      <c r="B15" s="20"/>
+      <c r="B15" s="34"/>
       <c r="C15" s="11">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>86</v>
@@ -1956,12 +2078,15 @@
       <c r="K15" s="13" t="s">
         <v>200</v>
       </c>
-    </row>
-    <row r="16" spans="1:21" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="26" t="s">
+      <c r="L15" s="13" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" s="6" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="35" t="s">
         <v>9</v>
       </c>
-      <c r="B16" s="26"/>
+      <c r="B16" s="35"/>
       <c r="C16" s="11">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -1970,34 +2095,34 @@
         <v>199</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A17" s="16" t="s">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A17" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="B17" s="16"/>
+      <c r="B17" s="17"/>
       <c r="C17" s="11">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A18" s="17" t="s">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A18" s="21" t="s">
         <v>14</v>
       </c>
-      <c r="B18" s="17"/>
+      <c r="B18" s="21"/>
       <c r="C18" s="11">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="19" t="s">
+    <row r="19" spans="1:12" s="5" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="33" t="s">
         <v>15</v>
       </c>
-      <c r="B19" s="19"/>
+      <c r="B19" s="33"/>
       <c r="C19" s="11">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H19" s="5" t="s">
         <v>148</v>
@@ -2011,12 +2136,15 @@
       <c r="K19" s="5" t="s">
         <v>195</v>
       </c>
-    </row>
-    <row r="20" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="26" t="s">
+      <c r="L19" s="5" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" s="6" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="35" t="s">
         <v>16</v>
       </c>
-      <c r="B20" s="26"/>
+      <c r="B20" s="35"/>
       <c r="C20" s="11">
         <f t="shared" si="0"/>
         <v>2</v>
@@ -2028,24 +2156,27 @@
         <v>157</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A21" s="16" t="s">
+    <row r="21" spans="1:12" s="42" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="40" t="s">
         <v>17</v>
       </c>
-      <c r="B21" s="16"/>
-      <c r="C21" s="11">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="K21" t="s">
+      <c r="B21" s="40"/>
+      <c r="C21" s="41">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="K21" s="42" t="s">
         <v>198</v>
       </c>
-    </row>
-    <row r="22" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="19" t="s">
+      <c r="L21" s="42" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" s="5" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="33" t="s">
         <v>19</v>
       </c>
-      <c r="B22" s="19"/>
+      <c r="B22" s="33"/>
       <c r="C22" s="11">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -2060,14 +2191,14 @@
         <v>192</v>
       </c>
     </row>
-    <row r="23" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="19" t="s">
+    <row r="23" spans="1:12" s="5" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="33" t="s">
         <v>20</v>
       </c>
-      <c r="B23" s="19"/>
+      <c r="B23" s="33"/>
       <c r="C23" s="11">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F23" s="5" t="s">
         <v>105</v>
@@ -2078,15 +2209,18 @@
       <c r="I23" s="5" t="s">
         <v>154</v>
       </c>
-    </row>
-    <row r="24" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="19" t="s">
+      <c r="L23" s="5" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" s="5" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="B24" s="19"/>
+      <c r="B24" s="33"/>
       <c r="C24" s="11">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G24" s="5" t="s">
         <v>112</v>
@@ -2100,15 +2234,18 @@
       <c r="K24" s="5" t="s">
         <v>196</v>
       </c>
-    </row>
-    <row r="25" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="25" t="s">
+      <c r="L24" s="5" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" s="5" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="39" t="s">
         <v>18</v>
       </c>
-      <c r="B25" s="25"/>
+      <c r="B25" s="39"/>
       <c r="C25" s="11">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E25" s="5" t="s">
         <v>98</v>
@@ -2125,12 +2262,15 @@
       <c r="K25" s="5" t="s">
         <v>153</v>
       </c>
-    </row>
-    <row r="26" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="19" t="s">
+      <c r="L25" s="5" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" s="5" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="B26" s="19"/>
+      <c r="B26" s="33"/>
       <c r="C26" s="11">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -2148,59 +2288,59 @@
         <v>193</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A27" s="17" t="s">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A27" s="21" t="s">
         <v>24</v>
       </c>
-      <c r="B27" s="17"/>
+      <c r="B27" s="21"/>
       <c r="C27" s="11">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A28" s="17" t="s">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A28" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="B28" s="17"/>
+      <c r="B28" s="21"/>
       <c r="C28" s="11">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A29" s="22" t="s">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A29" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="B29" s="22"/>
+      <c r="B29" s="27"/>
       <c r="C29" s="11">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A30" s="22"/>
-      <c r="B30" s="22"/>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A30" s="27"/>
+      <c r="B30" s="27"/>
       <c r="C30" s="11">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="16" t="s">
+    <row r="31" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="B31" s="16"/>
+      <c r="B31" s="17"/>
       <c r="C31" s="11">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="28" t="s">
+    <row r="32" spans="1:12" s="8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="31" t="s">
         <v>28</v>
       </c>
-      <c r="B32" s="28"/>
+      <c r="B32" s="31"/>
       <c r="C32" s="11">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -2209,14 +2349,14 @@
         <v>135</v>
       </c>
     </row>
-    <row r="33" spans="1:11" s="8" customFormat="1" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="28" t="s">
+    <row r="33" spans="1:12" s="8" customFormat="1" ht="17.7" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="31" t="s">
         <v>29</v>
       </c>
-      <c r="B33" s="28"/>
+      <c r="B33" s="31"/>
       <c r="C33" s="11">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H33" s="8" t="s">
         <v>138</v>
@@ -2224,12 +2364,15 @@
       <c r="K33" s="8" t="s">
         <v>202</v>
       </c>
-    </row>
-    <row r="34" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="28" t="s">
+      <c r="L33" s="8" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" s="8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="31" t="s">
         <v>30</v>
       </c>
-      <c r="B34" s="28"/>
+      <c r="B34" s="31"/>
       <c r="C34" s="11">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -2244,11 +2387,11 @@
         <v>201</v>
       </c>
     </row>
-    <row r="35" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="28" t="s">
+    <row r="35" spans="1:12" s="8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="31" t="s">
         <v>31</v>
       </c>
-      <c r="B35" s="28"/>
+      <c r="B35" s="31"/>
       <c r="C35" s="11">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -2257,24 +2400,24 @@
         <v>159</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A36" s="16" t="s">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A36" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="B36" s="16"/>
+      <c r="B36" s="17"/>
       <c r="C36" s="11">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="27" t="s">
+    <row r="37" spans="1:12" s="8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A37" s="30" t="s">
         <v>33</v>
       </c>
-      <c r="B37" s="27"/>
+      <c r="B37" s="30"/>
       <c r="C37" s="11">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H37" s="8" t="s">
         <v>139</v>
@@ -2285,12 +2428,15 @@
       <c r="K37" s="8" t="s">
         <v>203</v>
       </c>
-    </row>
-    <row r="38" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="27" t="s">
+      <c r="L37" s="8" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" s="8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A38" s="30" t="s">
         <v>34</v>
       </c>
-      <c r="B38" s="27"/>
+      <c r="B38" s="30"/>
       <c r="C38" s="11">
         <f t="shared" si="0"/>
         <v>2</v>
@@ -2302,14 +2448,14 @@
         <v>204</v>
       </c>
     </row>
-    <row r="39" spans="1:11" s="14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:12" s="14" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A39" s="29" t="s">
         <v>35</v>
       </c>
       <c r="B39" s="29"/>
       <c r="C39" s="11">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D39" s="14" t="s">
         <v>90</v>
@@ -2335,15 +2481,18 @@
       <c r="K39" s="14" t="s">
         <v>208</v>
       </c>
-    </row>
-    <row r="40" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="27" t="s">
+      <c r="L39" s="14" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" s="8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A40" s="30" t="s">
         <v>36</v>
       </c>
-      <c r="B40" s="27"/>
+      <c r="B40" s="30"/>
       <c r="C40" s="11">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E40" s="8" t="s">
         <v>103</v>
@@ -2360,38 +2509,44 @@
       <c r="K40" s="8" t="s">
         <v>234</v>
       </c>
-    </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A41" s="16" t="s">
+      <c r="L40" s="8" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A41" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="B41" s="16"/>
+      <c r="B41" s="17"/>
       <c r="C41" s="11">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A42" s="30" t="s">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A42" s="23" t="s">
         <v>38</v>
       </c>
-      <c r="B42" s="30"/>
+      <c r="B42" s="23"/>
       <c r="C42" s="11">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A43" s="30" t="s">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A43" s="23" t="s">
         <v>39</v>
       </c>
-      <c r="B43" s="30"/>
+      <c r="B43" s="23"/>
       <c r="C43" s="11">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="1:11" s="14" customFormat="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="L43" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12" s="14" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A44" s="29" t="s">
         <v>40</v>
       </c>
@@ -2413,7 +2568,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="45" spans="1:11" s="14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:12" s="14" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A45" s="29" t="s">
         <v>41</v>
       </c>
@@ -2438,21 +2593,21 @@
         <v>230</v>
       </c>
     </row>
-    <row r="46" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="16" t="s">
+    <row r="46" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A46" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="B46" s="16"/>
+      <c r="B46" s="17"/>
       <c r="C46" s="11">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:11" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="31" t="s">
+    <row r="47" spans="1:12" s="9" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A47" s="32" t="s">
         <v>43</v>
       </c>
-      <c r="B47" s="31"/>
+      <c r="B47" s="32"/>
       <c r="C47" s="11">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -2461,11 +2616,11 @@
         <v>123</v>
       </c>
     </row>
-    <row r="48" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="27" t="s">
+    <row r="48" spans="1:12" s="8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A48" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="B48" s="27"/>
+      <c r="B48" s="30"/>
       <c r="C48" s="11">
         <f t="shared" si="0"/>
         <v>2</v>
@@ -2477,11 +2632,11 @@
         <v>94</v>
       </c>
     </row>
-    <row r="49" spans="1:11" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="31" t="s">
+    <row r="49" spans="1:12" s="9" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A49" s="32" t="s">
         <v>45</v>
       </c>
-      <c r="B49" s="31"/>
+      <c r="B49" s="32"/>
       <c r="C49" s="11">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -2490,34 +2645,34 @@
         <v>145</v>
       </c>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A50" s="30" t="s">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A50" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="B50" s="30"/>
+      <c r="B50" s="23"/>
       <c r="C50" s="11">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A51" s="16" t="s">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A51" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="B51" s="16"/>
+      <c r="B51" s="17"/>
       <c r="C51" s="11">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="27" t="s">
+    <row r="52" spans="1:12" s="8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A52" s="30" t="s">
         <v>48</v>
       </c>
-      <c r="B52" s="27"/>
+      <c r="B52" s="30"/>
       <c r="C52" s="11">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D52" s="8" t="s">
         <v>92</v>
@@ -2525,12 +2680,15 @@
       <c r="E52" s="8" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="53" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="27" t="s">
+      <c r="L52" s="8" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12" s="8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A53" s="30" t="s">
         <v>49</v>
       </c>
-      <c r="B53" s="27"/>
+      <c r="B53" s="30"/>
       <c r="C53" s="11">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -2545,14 +2703,14 @@
         <v>206</v>
       </c>
     </row>
-    <row r="54" spans="1:11" s="14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:12" s="14" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A54" s="29" t="s">
         <v>50</v>
       </c>
       <c r="B54" s="29"/>
       <c r="C54" s="11">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D54" s="14" t="s">
         <v>88</v>
@@ -2566,12 +2724,15 @@
       <c r="J54" s="14" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="55" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="27" t="s">
+      <c r="L54" s="14" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12" s="10" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A55" s="30" t="s">
         <v>51</v>
       </c>
-      <c r="B55" s="27"/>
+      <c r="B55" s="30"/>
       <c r="C55" s="11">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -2586,21 +2747,21 @@
         <v>207</v>
       </c>
     </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A56" s="16" t="s">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A56" s="17" t="s">
         <v>52</v>
       </c>
-      <c r="B56" s="16"/>
+      <c r="B56" s="17"/>
       <c r="C56" s="11">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="27" t="s">
+    <row r="57" spans="1:12" s="8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A57" s="30" t="s">
         <v>53</v>
       </c>
-      <c r="B57" s="27"/>
+      <c r="B57" s="30"/>
       <c r="C57" s="11">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -2615,11 +2776,11 @@
         <v>205</v>
       </c>
     </row>
-    <row r="58" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="27" t="s">
+    <row r="58" spans="1:12" s="8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A58" s="30" t="s">
         <v>54</v>
       </c>
-      <c r="B58" s="27"/>
+      <c r="B58" s="30"/>
       <c r="C58" s="11">
         <f t="shared" si="0"/>
         <v>2</v>
@@ -2631,14 +2792,14 @@
         <v>97</v>
       </c>
     </row>
-    <row r="59" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="27" t="s">
+    <row r="59" spans="1:12" s="8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A59" s="30" t="s">
         <v>55</v>
       </c>
-      <c r="B59" s="27"/>
+      <c r="B59" s="30"/>
       <c r="C59" s="11">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H59" s="8" t="s">
         <v>136</v>
@@ -2649,40 +2810,43 @@
       <c r="J59" s="8" t="s">
         <v>178</v>
       </c>
-    </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A60" s="34" t="s">
+      <c r="L59" s="8" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="60" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A60" s="28" t="s">
         <v>56</v>
       </c>
-      <c r="B60" s="34"/>
+      <c r="B60" s="28"/>
       <c r="C60" s="11">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A61" s="34"/>
-      <c r="B61" s="34"/>
+    <row r="61" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A61" s="28"/>
+      <c r="B61" s="28"/>
       <c r="C61" s="11">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A62" s="16" t="s">
+    <row r="62" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A62" s="17" t="s">
         <v>57</v>
       </c>
-      <c r="B62" s="16"/>
+      <c r="B62" s="17"/>
       <c r="C62" s="11">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="18" t="s">
+    <row r="63" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A63" s="16" t="s">
         <v>186</v>
       </c>
-      <c r="B63" s="18"/>
+      <c r="B63" s="16"/>
       <c r="C63" s="11">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -2697,27 +2861,30 @@
         <v>209</v>
       </c>
     </row>
-    <row r="64" spans="1:11" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="35" t="s">
+    <row r="64" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A64" s="22" t="s">
         <v>58</v>
       </c>
-      <c r="B64" s="35"/>
+      <c r="B64" s="22"/>
       <c r="C64" s="11">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H64" s="4" t="s">
         <v>144</v>
       </c>
-    </row>
-    <row r="65" spans="1:11" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="36" t="s">
+      <c r="L64" s="4" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="65" spans="1:12" s="15" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A65" s="26" t="s">
         <v>59</v>
       </c>
-      <c r="B65" s="36"/>
+      <c r="B65" s="26"/>
       <c r="C65" s="11">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F65" s="15" t="s">
         <v>116</v>
@@ -2731,12 +2898,15 @@
       <c r="J65" s="15" t="s">
         <v>184</v>
       </c>
-    </row>
-    <row r="66" spans="1:11" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="35" t="s">
+      <c r="L65" s="15" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="66" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A66" s="22" t="s">
         <v>60</v>
       </c>
-      <c r="B66" s="35"/>
+      <c r="B66" s="22"/>
       <c r="C66" s="11">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -2745,34 +2915,34 @@
         <v>182</v>
       </c>
     </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A67" s="16" t="s">
+    <row r="67" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A67" s="17" t="s">
         <v>61</v>
       </c>
-      <c r="B67" s="16"/>
+      <c r="B67" s="17"/>
       <c r="C67" s="11">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A68" s="30" t="s">
+    <row r="68" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A68" s="23" t="s">
         <v>62</v>
       </c>
-      <c r="B68" s="30"/>
+      <c r="B68" s="23"/>
       <c r="C68" s="11">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="18" t="s">
+    <row r="69" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A69" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="B69" s="18"/>
+      <c r="B69" s="16"/>
       <c r="C69" s="11">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H69" s="2" t="s">
         <v>146</v>
@@ -2783,12 +2953,15 @@
       <c r="K69" s="2" t="s">
         <v>213</v>
       </c>
-    </row>
-    <row r="70" spans="1:11" s="2" customFormat="1" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="A70" s="18" t="s">
+      <c r="L69" s="2" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="70" spans="1:12" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.35">
+      <c r="A70" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="B70" s="18"/>
+      <c r="B70" s="16"/>
       <c r="C70" s="11">
         <f t="shared" si="0"/>
         <v>2</v>
@@ -2800,21 +2973,21 @@
         <v>183</v>
       </c>
     </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A71" s="33" t="s">
+    <row r="71" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A71" s="24" t="s">
         <v>65</v>
       </c>
-      <c r="B71" s="33"/>
+      <c r="B71" s="24"/>
       <c r="C71" s="11">
         <f t="shared" ref="C71:C93" si="1">COUNTA(D71:U71)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="32" t="s">
+    <row r="72" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A72" s="25" t="s">
         <v>66</v>
       </c>
-      <c r="B72" s="32"/>
+      <c r="B72" s="25"/>
       <c r="C72" s="11">
         <f t="shared" si="1"/>
         <v>1</v>
@@ -2823,11 +2996,11 @@
         <v>211</v>
       </c>
     </row>
-    <row r="73" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="32" t="s">
+    <row r="73" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A73" s="25" t="s">
         <v>67</v>
       </c>
-      <c r="B73" s="32"/>
+      <c r="B73" s="25"/>
       <c r="C73" s="11">
         <f t="shared" si="1"/>
         <v>1</v>
@@ -2836,21 +3009,21 @@
         <v>125</v>
       </c>
     </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A74" s="33" t="s">
+    <row r="74" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A74" s="24" t="s">
         <v>68</v>
       </c>
-      <c r="B74" s="33"/>
+      <c r="B74" s="24"/>
       <c r="C74" s="11">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="32" t="s">
+    <row r="75" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A75" s="25" t="s">
         <v>69</v>
       </c>
-      <c r="B75" s="32"/>
+      <c r="B75" s="25"/>
       <c r="C75" s="11">
         <f t="shared" si="1"/>
         <v>1</v>
@@ -2859,77 +3032,83 @@
         <v>87</v>
       </c>
     </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A76" s="30" t="s">
+    <row r="76" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A76" s="23" t="s">
         <v>70</v>
       </c>
-      <c r="B76" s="30"/>
+      <c r="B76" s="23"/>
       <c r="C76" s="11">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="32" t="s">
+    <row r="77" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A77" s="25" t="s">
         <v>71</v>
       </c>
-      <c r="B77" s="32"/>
+      <c r="B77" s="25"/>
       <c r="C77" s="11">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F77" s="1" t="s">
         <v>113</v>
       </c>
-    </row>
-    <row r="78" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="32" t="s">
+      <c r="L77" s="1" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="78" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A78" s="25" t="s">
         <v>72</v>
       </c>
-      <c r="B78" s="32"/>
+      <c r="B78" s="25"/>
       <c r="C78" s="11">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F78" s="1" t="s">
         <v>113</v>
       </c>
-    </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A79" s="17" t="s">
+      <c r="L78" s="1" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="79" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A79" s="21" t="s">
         <v>73</v>
       </c>
-      <c r="B79" s="17"/>
+      <c r="B79" s="21"/>
       <c r="C79" s="11">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A80" s="17" t="s">
+    <row r="80" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A80" s="21" t="s">
         <v>177</v>
       </c>
-      <c r="B80" s="17"/>
+      <c r="B80" s="21"/>
       <c r="C80" s="11">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A81" s="16" t="s">
+    <row r="81" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A81" s="17" t="s">
         <v>74</v>
       </c>
-      <c r="B81" s="16"/>
+      <c r="B81" s="17"/>
       <c r="C81" s="11">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:11" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="36" t="s">
+    <row r="82" spans="1:12" s="15" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A82" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="B82" s="36"/>
+      <c r="B82" s="26"/>
       <c r="C82" s="11">
         <f t="shared" si="1"/>
         <v>4</v>
@@ -2947,14 +3126,14 @@
         <v>215</v>
       </c>
     </row>
-    <row r="83" spans="1:11" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="36" t="s">
+    <row r="83" spans="1:12" s="15" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A83" s="26" t="s">
         <v>76</v>
       </c>
-      <c r="B83" s="36"/>
+      <c r="B83" s="26"/>
       <c r="C83" s="11">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F83" s="15" t="s">
         <v>115</v>
@@ -2968,35 +3147,44 @@
       <c r="K83" s="15" t="s">
         <v>214</v>
       </c>
-    </row>
-    <row r="84" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A84" s="33" t="s">
+      <c r="L83" s="15" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="84" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A84" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="B84" s="33"/>
+      <c r="B84" s="24"/>
       <c r="C84" s="11">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="85" spans="1:11" s="2" customFormat="1" ht="13.35" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A85" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="K84" t="s">
+        <v>254</v>
+      </c>
+      <c r="L84" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="85" spans="1:12" s="2" customFormat="1" ht="13.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A85" s="16" t="s">
         <v>220</v>
       </c>
-      <c r="B85" s="18"/>
+      <c r="B85" s="16"/>
       <c r="C85" s="11">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:11" s="2" customFormat="1" ht="13.35" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A86" s="18" t="s">
+    <row r="86" spans="1:12" s="2" customFormat="1" ht="13.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A86" s="16" t="s">
         <v>221</v>
       </c>
-      <c r="B86" s="18"/>
+      <c r="B86" s="16"/>
       <c r="C86" s="11">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I86" s="2" t="s">
         <v>171</v>
@@ -3004,12 +3192,15 @@
       <c r="K86" s="2" t="s">
         <v>216</v>
       </c>
-    </row>
-    <row r="87" spans="1:11" s="2" customFormat="1" ht="13.35" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A87" s="18" t="s">
+      <c r="L86" s="2" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="87" spans="1:12" s="2" customFormat="1" ht="13.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A87" s="16" t="s">
         <v>224</v>
       </c>
-      <c r="B87" s="18"/>
+      <c r="B87" s="16"/>
       <c r="C87" s="11">
         <f t="shared" si="1"/>
         <v>2</v>
@@ -3021,41 +3212,41 @@
         <v>210</v>
       </c>
     </row>
-    <row r="88" spans="1:11" s="2" customFormat="1" ht="13.35" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A88" s="18" t="s">
+    <row r="88" spans="1:12" s="2" customFormat="1" ht="13.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A88" s="16" t="s">
         <v>223</v>
       </c>
-      <c r="B88" s="18"/>
+      <c r="B88" s="16"/>
       <c r="C88" s="11">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:11" s="2" customFormat="1" ht="13.35" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A89" s="18" t="s">
+    <row r="89" spans="1:12" s="2" customFormat="1" ht="13.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A89" s="16" t="s">
         <v>222</v>
       </c>
-      <c r="B89" s="18"/>
+      <c r="B89" s="16"/>
       <c r="C89" s="11">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:11" ht="13.35" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A90" s="33" t="s">
+    <row r="90" spans="1:12" ht="13.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A90" s="24" t="s">
         <v>78</v>
       </c>
-      <c r="B90" s="33"/>
+      <c r="B90" s="24"/>
       <c r="C90" s="11">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:11" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A91" s="35" t="s">
+    <row r="91" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A91" s="22" t="s">
         <v>79</v>
       </c>
-      <c r="B91" s="35"/>
+      <c r="B91" s="22"/>
       <c r="C91" s="11">
         <f t="shared" si="1"/>
         <v>3</v>
@@ -3070,24 +3261,27 @@
         <v>97</v>
       </c>
     </row>
-    <row r="92" spans="1:11" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A92" s="35" t="s">
+    <row r="92" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A92" s="22" t="s">
         <v>80</v>
       </c>
-      <c r="B92" s="35"/>
+      <c r="B92" s="22"/>
       <c r="C92" s="11">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I92" s="4" t="s">
         <v>160</v>
       </c>
-    </row>
-    <row r="93" spans="1:11" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A93" s="35" t="s">
+      <c r="L92" s="4" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="93" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A93" s="22" t="s">
         <v>81</v>
       </c>
-      <c r="B93" s="35"/>
+      <c r="B93" s="22"/>
       <c r="C93" s="11">
         <f t="shared" si="1"/>
         <v>2</v>
@@ -3099,78 +3293,168 @@
         <v>212</v>
       </c>
     </row>
-    <row r="94" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A94" s="30"/>
-      <c r="B94" s="30"/>
-    </row>
-    <row r="95" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A95" s="17"/>
-      <c r="B95" s="17"/>
-    </row>
-    <row r="96" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A96" s="17"/>
-      <c r="B96" s="17"/>
-    </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A97" s="17"/>
-      <c r="B97" s="17"/>
-    </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A98" s="39" t="s">
+    <row r="94" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A94" s="23"/>
+      <c r="B94" s="23"/>
+    </row>
+    <row r="95" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A95" s="21"/>
+      <c r="B95" s="21"/>
+    </row>
+    <row r="96" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A96" s="21"/>
+      <c r="B96" s="21"/>
+    </row>
+    <row r="97" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A97" s="21"/>
+      <c r="B97" s="21"/>
+    </row>
+    <row r="98" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A98" s="20" t="s">
         <v>235</v>
       </c>
-      <c r="B98" s="39"/>
-    </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A99" s="39"/>
-      <c r="B99" s="39"/>
-    </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A100" s="37" t="s">
+      <c r="B98" s="20"/>
+    </row>
+    <row r="99" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A99" s="20"/>
+      <c r="B99" s="20"/>
+    </row>
+    <row r="100" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A100" s="18" t="s">
         <v>217</v>
       </c>
-      <c r="B100" s="38"/>
-    </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A101" s="38"/>
-      <c r="B101" s="38"/>
-    </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A102" s="38"/>
-      <c r="B102" s="38"/>
-    </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A103" s="38"/>
-      <c r="B103" s="38"/>
-    </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A104" s="38"/>
-      <c r="B104" s="38"/>
-    </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A105" s="37" t="s">
+      <c r="B100" s="19"/>
+    </row>
+    <row r="101" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A101" s="19"/>
+      <c r="B101" s="19"/>
+    </row>
+    <row r="102" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A102" s="19"/>
+      <c r="B102" s="19"/>
+    </row>
+    <row r="103" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A103" s="19"/>
+      <c r="B103" s="19"/>
+    </row>
+    <row r="104" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A104" s="19"/>
+      <c r="B104" s="19"/>
+    </row>
+    <row r="105" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A105" s="18" t="s">
         <v>218</v>
       </c>
-      <c r="B105" s="38"/>
-    </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A106" s="38"/>
-      <c r="B106" s="38"/>
-    </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A107" s="38"/>
-      <c r="B107" s="38"/>
-    </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A108" s="38"/>
-      <c r="B108" s="38"/>
-    </row>
-    <row r="109" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A109" s="38"/>
-      <c r="B109" s="38"/>
+      <c r="B105" s="19"/>
+    </row>
+    <row r="106" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A106" s="19"/>
+      <c r="B106" s="19"/>
+    </row>
+    <row r="107" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A107" s="19"/>
+      <c r="B107" s="19"/>
+    </row>
+    <row r="108" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A108" s="19"/>
+      <c r="B108" s="19"/>
+    </row>
+    <row r="109" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A109" s="19"/>
+      <c r="B109" s="19"/>
     </row>
   </sheetData>
   <mergeCells count="114">
+    <mergeCell ref="J1:J2"/>
+    <mergeCell ref="A80:B80"/>
+    <mergeCell ref="A89:B89"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="A3:B4"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="A59:B59"/>
+    <mergeCell ref="A53:B53"/>
+    <mergeCell ref="A51:B51"/>
+    <mergeCell ref="A52:B52"/>
+    <mergeCell ref="A41:B41"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="A34:B34"/>
+    <mergeCell ref="A35:B35"/>
+    <mergeCell ref="A36:B36"/>
+    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="A38:B38"/>
+    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="A40:B40"/>
+    <mergeCell ref="A42:B42"/>
+    <mergeCell ref="A43:B43"/>
+    <mergeCell ref="A44:B44"/>
+    <mergeCell ref="A45:B45"/>
+    <mergeCell ref="A46:B46"/>
+    <mergeCell ref="A47:B47"/>
+    <mergeCell ref="A48:B48"/>
+    <mergeCell ref="A49:B49"/>
+    <mergeCell ref="A50:B50"/>
+    <mergeCell ref="A87:B87"/>
+    <mergeCell ref="A86:B86"/>
+    <mergeCell ref="A72:B72"/>
+    <mergeCell ref="A74:B74"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="A29:B30"/>
+    <mergeCell ref="A60:B61"/>
+    <mergeCell ref="A73:B73"/>
+    <mergeCell ref="A66:B66"/>
+    <mergeCell ref="A67:B67"/>
+    <mergeCell ref="A68:B68"/>
+    <mergeCell ref="A69:B69"/>
+    <mergeCell ref="A70:B70"/>
+    <mergeCell ref="A71:B71"/>
+    <mergeCell ref="A62:B62"/>
+    <mergeCell ref="A63:B63"/>
+    <mergeCell ref="A64:B64"/>
+    <mergeCell ref="A65:B65"/>
+    <mergeCell ref="A54:B54"/>
+    <mergeCell ref="A55:B55"/>
+    <mergeCell ref="A56:B56"/>
+    <mergeCell ref="A57:B57"/>
+    <mergeCell ref="A58:B58"/>
+    <mergeCell ref="A76:B76"/>
+    <mergeCell ref="A77:B77"/>
+    <mergeCell ref="A78:B78"/>
+    <mergeCell ref="A79:B79"/>
+    <mergeCell ref="A81:B81"/>
+    <mergeCell ref="A82:B82"/>
+    <mergeCell ref="A83:B83"/>
+    <mergeCell ref="A84:B84"/>
+    <mergeCell ref="A85:B85"/>
     <mergeCell ref="A88:B88"/>
     <mergeCell ref="U1:U2"/>
     <mergeCell ref="A100:B104"/>
@@ -3195,96 +3479,6 @@
     <mergeCell ref="A96:B96"/>
     <mergeCell ref="A90:B90"/>
     <mergeCell ref="A75:B75"/>
-    <mergeCell ref="A76:B76"/>
-    <mergeCell ref="A77:B77"/>
-    <mergeCell ref="A78:B78"/>
-    <mergeCell ref="A79:B79"/>
-    <mergeCell ref="A81:B81"/>
-    <mergeCell ref="A82:B82"/>
-    <mergeCell ref="A83:B83"/>
-    <mergeCell ref="A84:B84"/>
-    <mergeCell ref="A85:B85"/>
-    <mergeCell ref="A87:B87"/>
-    <mergeCell ref="A86:B86"/>
-    <mergeCell ref="A72:B72"/>
-    <mergeCell ref="A74:B74"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="A29:B30"/>
-    <mergeCell ref="A60:B61"/>
-    <mergeCell ref="A73:B73"/>
-    <mergeCell ref="A66:B66"/>
-    <mergeCell ref="A67:B67"/>
-    <mergeCell ref="A68:B68"/>
-    <mergeCell ref="A69:B69"/>
-    <mergeCell ref="A70:B70"/>
-    <mergeCell ref="A71:B71"/>
-    <mergeCell ref="A62:B62"/>
-    <mergeCell ref="A63:B63"/>
-    <mergeCell ref="A64:B64"/>
-    <mergeCell ref="A65:B65"/>
-    <mergeCell ref="A54:B54"/>
-    <mergeCell ref="A55:B55"/>
-    <mergeCell ref="A56:B56"/>
-    <mergeCell ref="A57:B57"/>
-    <mergeCell ref="A58:B58"/>
-    <mergeCell ref="A59:B59"/>
-    <mergeCell ref="A53:B53"/>
-    <mergeCell ref="A51:B51"/>
-    <mergeCell ref="A52:B52"/>
-    <mergeCell ref="A41:B41"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="A34:B34"/>
-    <mergeCell ref="A35:B35"/>
-    <mergeCell ref="A36:B36"/>
-    <mergeCell ref="A37:B37"/>
-    <mergeCell ref="A38:B38"/>
-    <mergeCell ref="A39:B39"/>
-    <mergeCell ref="A40:B40"/>
-    <mergeCell ref="A42:B42"/>
-    <mergeCell ref="A43:B43"/>
-    <mergeCell ref="A44:B44"/>
-    <mergeCell ref="A45:B45"/>
-    <mergeCell ref="A46:B46"/>
-    <mergeCell ref="A47:B47"/>
-    <mergeCell ref="A48:B48"/>
-    <mergeCell ref="A49:B49"/>
-    <mergeCell ref="A50:B50"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="J1:J2"/>
-    <mergeCell ref="A80:B80"/>
-    <mergeCell ref="A89:B89"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="A3:B4"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A12:B12"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <hyperlinks>

--- a/真题/考点分布.xlsx
+++ b/真题/考点分布.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\HIT837\HIT837-Book-of-Answer\真题\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B519EAE1-0257-4683-89B8-BA5366D898B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7523BD5B-C3C0-4957-BDC9-E3EA0C9606CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13320" xr2:uid="{483410DF-229B-F841-A2F7-CB7B2A2D44F9}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="260">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="259">
   <si>
     <t>考频</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -998,18 +998,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>时延计算 MTU</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>子网划分</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>快重传、字段功能</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve">connect API </t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1033,10 +1025,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>简述数字签名的工作流程</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 主机防火墙应用与独立防火墙</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1070,6 +1058,14 @@
   </si>
   <si>
     <t>AC计算</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>时延计算 ，MTU</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>快重传，字段功能</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2079,7 +2075,7 @@
         <v>200</v>
       </c>
       <c r="L15" s="13" t="s">
-        <v>243</v>
+        <v>258</v>
       </c>
     </row>
     <row r="16" spans="1:21" s="6" customFormat="1" x14ac:dyDescent="0.35">
@@ -2137,7 +2133,7 @@
         <v>195</v>
       </c>
       <c r="L19" s="5" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
     </row>
     <row r="20" spans="1:12" s="6" customFormat="1" x14ac:dyDescent="0.35">
@@ -2169,7 +2165,7 @@
         <v>198</v>
       </c>
       <c r="L21" s="42" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="22" spans="1:12" s="5" customFormat="1" x14ac:dyDescent="0.35">
@@ -2263,7 +2259,7 @@
         <v>153</v>
       </c>
       <c r="L25" s="5" t="s">
-        <v>241</v>
+        <v>257</v>
       </c>
     </row>
     <row r="26" spans="1:12" s="5" customFormat="1" x14ac:dyDescent="0.35">
@@ -2365,7 +2361,7 @@
         <v>202</v>
       </c>
       <c r="L33" s="8" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="34" spans="1:12" s="8" customFormat="1" x14ac:dyDescent="0.35">
@@ -2429,7 +2425,7 @@
         <v>203</v>
       </c>
       <c r="L37" s="8" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
     </row>
     <row r="38" spans="1:12" s="8" customFormat="1" x14ac:dyDescent="0.35">
@@ -2482,7 +2478,7 @@
         <v>208</v>
       </c>
       <c r="L39" s="14" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
     </row>
     <row r="40" spans="1:12" s="8" customFormat="1" x14ac:dyDescent="0.35">
@@ -2510,7 +2506,7 @@
         <v>234</v>
       </c>
       <c r="L40" s="8" t="s">
-        <v>250</v>
+        <v>234</v>
       </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.35">
@@ -2543,7 +2539,7 @@
         <v>1</v>
       </c>
       <c r="L43" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="44" spans="1:12" s="14" customFormat="1" x14ac:dyDescent="0.35">
@@ -2681,7 +2677,7 @@
         <v>109</v>
       </c>
       <c r="L52" s="8" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
     </row>
     <row r="53" spans="1:12" s="8" customFormat="1" x14ac:dyDescent="0.35">
@@ -2725,7 +2721,7 @@
         <v>180</v>
       </c>
       <c r="L54" s="14" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
     </row>
     <row r="55" spans="1:12" s="10" customFormat="1" x14ac:dyDescent="0.35">
@@ -2811,7 +2807,7 @@
         <v>178</v>
       </c>
       <c r="L59" s="8" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.35">
@@ -2874,7 +2870,7 @@
         <v>144</v>
       </c>
       <c r="L64" s="4" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
     </row>
     <row r="65" spans="1:12" s="15" customFormat="1" x14ac:dyDescent="0.35">
@@ -2899,7 +2895,7 @@
         <v>184</v>
       </c>
       <c r="L65" s="15" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
     </row>
     <row r="66" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.35">
@@ -2954,7 +2950,7 @@
         <v>213</v>
       </c>
       <c r="L69" s="2" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
     </row>
     <row r="70" spans="1:12" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.35">
@@ -3055,7 +3051,7 @@
         <v>113</v>
       </c>
       <c r="L77" s="1" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
     </row>
     <row r="78" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.35">
@@ -3071,7 +3067,7 @@
         <v>113</v>
       </c>
       <c r="L78" s="1" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
     </row>
     <row r="79" spans="1:12" x14ac:dyDescent="0.35">
@@ -3148,7 +3144,7 @@
         <v>214</v>
       </c>
       <c r="L83" s="15" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
     </row>
     <row r="84" spans="1:12" x14ac:dyDescent="0.35">
@@ -3161,10 +3157,10 @@
         <v>2</v>
       </c>
       <c r="K84" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="L84" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
     </row>
     <row r="85" spans="1:12" s="2" customFormat="1" ht="13.4" customHeight="1" x14ac:dyDescent="0.35">
@@ -3274,7 +3270,7 @@
         <v>160</v>
       </c>
       <c r="L92" s="4" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="93" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.35">
